--- a/data/archive/2026-08-10-main-ledger-archived-shadow-primary/wnba.xlsx
+++ b/data/archive/2026-08-10-main-ledger-archived-shadow-primary/wnba.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS19" headerRowCount="1">
-  <autoFilter ref="A1:CS19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS26" headerRowCount="1">
+  <autoFilter ref="A1:CS26"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$19)</f>
+        <f>COUNTA('Picks'!$A$2:$A$26)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$19,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$26,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")+COUNTIFS('Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$19,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$26,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")/(COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"win")+COUNTIFS('Picks'!$BX$2:$BX$19,"&gt;0",'Picks'!$V$2:$V$19,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")/(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$19)/SUM('Picks'!$BX$2:$BX$19),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$26)/SUM('Picks'!$BX$2:$BX$26),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$19)</f>
+        <f>SUM('Picks'!$BY$2:$BY$26)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$19,"&lt;&gt;",'Picks'!$AB$2:$AB$19),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$26,"&lt;&gt;",'Picks'!$AB$2:$AB$26),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$19,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$19,'Picks'!$AM$2:$AM$19,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$26,'Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A14,'Picks'!$U$2:$U$19,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A15,'Picks'!$U$2:$U$19,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled",'Picks'!$V$2:$V$19,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$19,'Picks'!$H$2:$H$19,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$19,'Picks'!$H$2:$H$19,$A16,'Picks'!$U$2:$U$19,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS19"/>
+  <dimension ref="A1:CS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6619,12 +6619,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>1142ac42f2254e3c</t>
+          <t>b168d7d686c645e1</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:24:46.511596Z</t>
+          <t>2026-08-05T01:07:48.070985Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -6669,20 +6669,20 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>-733</v>
+        <v>-614</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.162866</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.859944</v>
       </c>
       <c r="O19" s="28" t="n">
         <v>0.774468</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>-0.105484</v>
+        <v>-0.085476</v>
       </c>
       <c r="R19" s="26" t="n">
         <v>0</v>
@@ -6697,21 +6697,35 @@
       </c>
       <c r="U19" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>92</v>
+      </c>
       <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n"/>
-      <c r="AD19" s="24" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:21:25.381491Z</t>
+        </is>
+      </c>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5001; executable ask 0.8800 (aec-wnba-tor-gsv-2026-08-04); model edge vs ask -0.1055.</t>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8600 (aec-wnba-tor-gsv-2026-08-04); model edge vs ask -0.0855.</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6830,7 +6844,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:23:15.869749Z</t>
+          <t>2026-08-05T01:07:13.594446Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6840,16 +6854,16 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>-733</v>
+        <v>-614</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>1.136426</v>
+        <v>1.162866</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.879952</v>
+        <v>0.859944</v>
       </c>
       <c r="BN19" s="28" t="n">
-        <v>0.871287</v>
+        <v>0.851485</v>
       </c>
       <c r="BO19" s="28" t="n"/>
       <c r="BP19" s="25" t="n"/>
@@ -6903,6 +6917,2105 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>bde24094fcd540e4</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:56:24.360448Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>401857123</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.561972</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>0.221836</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>79</v>
+      </c>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:03:09.389849Z</t>
+        </is>
+      </c>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.3400 (aec-wnba-atl-wsh-2026-08-07); model edge vs ask +0.2220.</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>wnba-atl</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>wnba-was</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>7527e38cbf3d298e</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:56:00.000131Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="BN20" s="28" t="n">
+        <v>0.336634</v>
+      </c>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="inlineStr">
+        <is>
+          <t>0.5839932663</t>
+        </is>
+      </c>
+      <c r="CD20" s="24" t="inlineStr">
+        <is>
+          <t>-1.592597</t>
+        </is>
+      </c>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="inlineStr">
+        <is>
+          <t>6.900454</t>
+        </is>
+      </c>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="inlineStr">
+        <is>
+          <t>0.561972</t>
+        </is>
+      </c>
+      <c r="CS20" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>6abb4415c15d45fe</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:59.410253Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T20:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>401857127</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.636385</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.136385</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>91</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>93</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:12:03.525470Z</t>
+        </is>
+      </c>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5000 (aec-wnba-sea-por-2026-08-08); model edge vs ask +0.1364. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>wnba-sea</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>wnba-por</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Portland Fire</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>c4f4370995132da0</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:41.814320Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN21" s="28" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="inlineStr">
+        <is>
+          <t>0.6792726129</t>
+        </is>
+      </c>
+      <c r="CD21" s="24" t="inlineStr">
+        <is>
+          <t>-3.251216</t>
+        </is>
+      </c>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ21" s="24" t="inlineStr">
+        <is>
+          <t>6.663423</t>
+        </is>
+      </c>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="inlineStr">
+        <is>
+          <t>0.636385</t>
+        </is>
+      </c>
+      <c r="CS21" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>21ce05a60e8d4051</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T13:59:23.763456Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T12:30:00-0400</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>401857128</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.513331</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.263331</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>71</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:24:25.527598Z</t>
+        </is>
+      </c>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.2500 (aec-wnba-lv-ny-2026-08-09); model edge vs ask +0.2633. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>wnba-lva</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>wnba-nyl</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>New York Liberty</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>326af12f4add44d3</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T13:58:13.130881Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>300</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BN22" s="28" t="n">
+        <v>0.247525</v>
+      </c>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="inlineStr">
+        <is>
+          <t>0.4879470816</t>
+        </is>
+      </c>
+      <c r="CD22" s="24" t="inlineStr">
+        <is>
+          <t>3.090342</t>
+        </is>
+      </c>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ22" s="24" t="inlineStr">
+        <is>
+          <t>-3.371641</t>
+        </is>
+      </c>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="inlineStr">
+        <is>
+          <t>0.513331</t>
+        </is>
+      </c>
+      <c r="CS22" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>9bb87c61647d4403</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:06:21.079905Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T15:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>401857129</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.695232</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.164716</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n">
+        <v>1.7699</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T23:28:57.101159Z</t>
+        </is>
+      </c>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5300 (aec-wnba-phx-wsh-2026-08-09); model edge vs ask +0.1652. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>wnba-phx</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Phoenix Mercury</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>wnba-was</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>Washington Mystics</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>28057b4491fbc31b</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:05:41.727182Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN23" s="28" t="n">
+        <v>0.524752</v>
+      </c>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="inlineStr">
+        <is>
+          <t>0.7723991943</t>
+        </is>
+      </c>
+      <c r="CD23" s="24" t="inlineStr">
+        <is>
+          <t>0.96982</t>
+        </is>
+      </c>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ23" s="24" t="inlineStr">
+        <is>
+          <t>6.116575</t>
+        </is>
+      </c>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="inlineStr">
+        <is>
+          <t>0.695232</t>
+        </is>
+      </c>
+      <c r="CS23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>cb2c0aa7c6c446e9</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:27:02.435009Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>401857131</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.68049</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>-0.01921</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n">
+        <v>0.7511</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T02:33:53.277745Z</t>
+        </is>
+      </c>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.7000 (aec-wnba-gsv-la-2026-08-09); model edge vs ask -0.0195. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>wnba-gsv</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>wnba-las</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Sparks</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>3f8776ef716da556</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:26:42.890552Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN24" s="28" t="n">
+        <v>0.693069</v>
+      </c>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="inlineStr">
+        <is>
+          <t>0.2620546512</t>
+        </is>
+      </c>
+      <c r="CD24" s="24" t="inlineStr">
+        <is>
+          <t>1.491968</t>
+        </is>
+      </c>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ24" s="24" t="inlineStr">
+        <is>
+          <t>-1.513705</t>
+        </is>
+      </c>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="inlineStr">
+        <is>
+          <t>0.68049</t>
+        </is>
+      </c>
+      <c r="CS24" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>84e168c081034099</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:34:47.251195Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T20:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>401857132</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.737133</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>-0.142819</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.8800 (aec-wnba-tor-atl-2026-08-10); model edge vs ask -0.1429. NOTE: NO_CALL_AVAILABILITY_SOURCE_CONFLICT unavailable for this game — defaulted to neutral, other features used normally.</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-tor</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Tempo</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-atl</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Dream</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>cc3e04aa2e66419b</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:34:14.661341Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-733</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.136426</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.879952</v>
+      </c>
+      <c r="BN25" s="28" t="n">
+        <v>0.871287</v>
+      </c>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="inlineStr">
+        <is>
+          <t>0.8354799774</t>
+        </is>
+      </c>
+      <c r="CD25" s="24" t="inlineStr">
+        <is>
+          <t>3.773711</t>
+        </is>
+      </c>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_AVAILABILITY_SOURCE_CONFLICT</t>
+        </is>
+      </c>
+      <c r="CJ25" s="24" t="inlineStr">
+        <is>
+          <t>-3.297793</t>
+        </is>
+      </c>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="inlineStr">
+        <is>
+          <t>0.737133</t>
+        </is>
+      </c>
+      <c r="CS25" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>a01d4ac1e5f74584</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:34:47.251195Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>401857133</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>WNBA</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.543228</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.012712</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.5001; executable ask 0.5300 (aec-wnba-chi-sea-2026-08-10); model edge vs ask +0.0132.</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-chi</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Sky</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-sea</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Storm</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>0f4dad8fd6dfb442</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:34:14.903004Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN26" s="28" t="n">
+        <v>0.524752</v>
+      </c>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="inlineStr">
+        <is>
+          <t>0.4387952332</t>
+        </is>
+      </c>
+      <c r="CD26" s="24" t="inlineStr">
+        <is>
+          <t>-0.915897</t>
+        </is>
+      </c>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="inlineStr">
+        <is>
+          <t>-5.749741</t>
+        </is>
+      </c>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="inlineStr">
+        <is>
+          <t>0.543228</t>
+        </is>
+      </c>
+      <c r="CS26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
